--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -786,6 +786,9 @@
       <c r="G2" t="str">
         <v>0101296551151010551055155552525665555515105555</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,109 +443,106 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+        <v>768_清香木_undefined_undefined_undefinedundefined</v>
       </c>
       <c r="F3" t="str">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+        <v>838_小菊罗西三文鱼_undefined_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="str">
-        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>2</v>
-      </c>
       <c r="C8" t="str">
-        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
       </c>
       <c r="F8" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
       </c>
       <c r="F9" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+        <v>115_绣球冰淇淋绿_Hydrangea Pointed Green_Hydrangea L._1stem</v>
       </c>
       <c r="F10" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
       </c>
       <c r="F11" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
         <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="str">
-        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F12" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
-        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
       </c>
       <c r="F13" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>3</v>
-      </c>
       <c r="C14" t="str">
-        <v>504_大花葱 直_Allium _undefined_1bunch</v>
+        <v>602_康乃馨白_white_undefined_20stems</v>
       </c>
       <c r="F14" t="str">
         <v>10</v>
@@ -553,18 +550,15 @@
     </row>
     <row r="15">
       <c r="C15" t="str">
-        <v>644_唐松草_undefined_undefined_1bunch</v>
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
       </c>
       <c r="F15" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>1</v>
-      </c>
       <c r="C16" t="str">
-        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
       </c>
       <c r="F16" t="str">
         <v>5</v>
@@ -572,164 +566,47 @@
     </row>
     <row r="17">
       <c r="C17" t="str">
-        <v>877_黄洋金边原色_undefined_undefined_1bunch</v>
+        <v>449_柔丽思 绿_undefined_undefined_1bunch</v>
       </c>
       <c r="F17" t="str">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" t="str">
-        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
+        <v>543_柔丽思红_undefined_undefined_1bunch</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>543_柔丽思红_undefined_undefined_1bunch</v>
+    <row r="19" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
       </c>
       <c r="F19" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" t="str">
-        <v>768_清香木_undefined_undefined_undefinedundefined</v>
+    <row r="20" xml:space="preserve">
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
       </c>
       <c r="F20" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
-      </c>
-      <c r="F21" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
-      </c>
-      <c r="F22" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
-light blue_undefined_1bunch</v>
-      </c>
-      <c r="F23" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
-dark blue_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="str">
-        <v>441_蓝星球_Echinops_undefined_1bunch</v>
-      </c>
-      <c r="F25" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F26" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>789_迷你菊浅粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F27" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="str">
-        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F28" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F29" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2</v>
-      </c>
-      <c r="C30" t="str">
-        <v>797_大菊黄_undefined_undefined_5stems</v>
-      </c>
-      <c r="F30" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="str">
-        <v>594_绿毛球_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>409_姜荷花 红_Curcuma red_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>423_鼠尾紫色_veronica purple_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="str">
-        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F35" t="str">
-        <v>5</v>
+    <row r="21" xml:space="preserve">
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -784,10 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101296551151010551055155552525665555515105555</v>
-      </c>
-      <c r="H2" t="str">
-        <v>CNY</v>
+        <v>020551010551020301051010555550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -603,6 +603,9 @@
         <v xml:space="preserve">542_吊米 红_hanging amaranthus
 red_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020551010551020301051010555550</v>
+        <v>020551010551020301051010555555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,90 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>110_绣球浅蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F28" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +745,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020551010551020301051010555555</v>
+        <v>02055101055102030105101055555510555510201050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -687,10 +687,308 @@
       <c r="A31" t="str">
         <v>3</v>
       </c>
+      <c r="C31" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>882_乒乓菊黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>476_酸浆果_Physalis_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>569_灯笼果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>513_松虫草粉白_scabiosa rainbow_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>5</v>
+      </c>
+      <c r="C38" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>6</v>
+      </c>
+      <c r="C43" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F43" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F44" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2</v>
+      </c>
+      <c r="C51" t="str">
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>823_剑兰阿贾克斯_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>115_绣球冰淇淋绿_Hydrangea Pointed Green_Hydrangea L._1stem</v>
+      </c>
+      <c r="F55" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>101_绣球浅秋红_Hydrangea Vintage Red_Hydrangea L._1stem</v>
+      </c>
+      <c r="F56" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>393_天堂鸟_strelitzia reginae_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>441_蓝星球_Echinops_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>3</v>
+      </c>
+      <c r="C60" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>788_国产直葱白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>4</v>
+      </c>
+      <c r="C62" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>5</v>
+      </c>
+      <c r="C64" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L64"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -745,7 +1043,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02055101055102030105101055555510555510201050</v>
+        <v>020551010551020301051010555555105555102010510101055105205105514151055101021010151025201010302010221810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-24.xlsx
@@ -1045,6 +1045,9 @@
       <c r="G2" t="str">
         <v>020551010551020301051010555555105555102010510101055105205105514151055101021010151025201010302010221810</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
